--- a/task/06_冷热源设备_01-03/01_冷水机组/水冷螺杆式冷水机组（单机）.xlsx
+++ b/task/06_冷热源设备_01-03/01_冷水机组/水冷螺杆式冷水机组（单机）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19590" windowHeight="6140"/>
+    <workbookView windowWidth="24930" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="50">
   <si>
     <t>型号</t>
   </si>
@@ -37,10 +37,97 @@
     <t>蒸发器管径</t>
   </si>
   <si>
+    <t>使用电源</t>
+  </si>
+  <si>
+    <t>制冷量KW</t>
+  </si>
+  <si>
+    <t>制冷量Kcal_h</t>
+  </si>
+  <si>
+    <t>运行电流A</t>
+  </si>
+  <si>
+    <t>冷冻水量m3_h</t>
+  </si>
+  <si>
+    <t>冷却水量m3_h</t>
+  </si>
+  <si>
+    <t>压缩机型式</t>
+  </si>
+  <si>
+    <t>压缩机数量PCS</t>
+  </si>
+  <si>
+    <t>压缩机启动方式</t>
+  </si>
+  <si>
+    <t>压缩机容量控制%</t>
+  </si>
+  <si>
+    <t>压缩机功率KW</t>
+  </si>
+  <si>
+    <t>冷冻油种类</t>
+  </si>
+  <si>
+    <t>冷冻油容量L</t>
+  </si>
+  <si>
+    <t>冷媒种类</t>
+  </si>
+  <si>
+    <t>冷媒控制方式</t>
+  </si>
+  <si>
+    <t>冷媒容量KG</t>
+  </si>
+  <si>
+    <t>蒸发器型式</t>
+  </si>
+  <si>
+    <t>冷凝器型式</t>
+  </si>
+  <si>
+    <t>保护装置</t>
+  </si>
+  <si>
+    <t>重量KG</t>
+  </si>
+  <si>
     <t>SPS-120W</t>
   </si>
   <si>
     <t>水冷螺杆式冷水机组（单机）</t>
+  </si>
+  <si>
+    <t>3Φ-380V-50Hz</t>
+  </si>
+  <si>
+    <t>半封闭螺杆式</t>
+  </si>
+  <si>
+    <t>Y-△</t>
+  </si>
+  <si>
+    <t>0,33,66,100或0,25,50,75,100</t>
+  </si>
+  <si>
+    <t>HBR-A01</t>
+  </si>
+  <si>
+    <t>R-22</t>
+  </si>
+  <si>
+    <t>感温式外部均压膨胀阀</t>
+  </si>
+  <si>
+    <t>壳管式</t>
+  </si>
+  <si>
+    <t>高低压开关,防冻保护,可溶栓/安全阀,过载保护装置,线圈过热保护器,温度自动保护开关等。</t>
   </si>
   <si>
     <t>SPS-160W</t>
@@ -86,8 +173,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -98,16 +185,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -122,14 +208,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,13 +223,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,45 +237,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,16 +253,23 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,8 +284,46 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,25 +338,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,157 +476,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,6 +529,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -462,15 +558,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -480,11 +567,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -522,23 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,145 +637,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1015,17 +1102,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:AA14"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="19.0909090909091" customWidth="1"/>
-    <col min="3" max="5" width="27.5454545454545" customWidth="1"/>
-    <col min="6" max="6" width="34.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="35.3636363636364" customWidth="1"/>
+    <col min="1" max="7" width="18.9090909090909" customWidth="1"/>
+    <col min="8" max="8" width="14.9090909090909" customWidth="1"/>
+    <col min="9" max="9" width="13.9090909090909" customWidth="1"/>
+    <col min="10" max="10" width="15.3636363636364" customWidth="1"/>
+    <col min="11" max="11" width="12.6363636363636" customWidth="1"/>
+    <col min="12" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="15.1818181818182" customWidth="1"/>
+    <col min="16" max="16" width="16.2727272727273" customWidth="1"/>
+    <col min="17" max="17" width="33.1818181818182" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="11.8181818181818" customWidth="1"/>
+    <col min="20" max="20" width="12.9090909090909" customWidth="1"/>
+    <col min="21" max="21" width="9.54545454545454" customWidth="1"/>
+    <col min="22" max="22" width="23" customWidth="1"/>
+    <col min="23" max="24" width="11.8181818181818" customWidth="1"/>
+    <col min="25" max="25" width="27.5454545454545" customWidth="1"/>
+    <col min="26" max="26" width="92.8181818181818" customWidth="1"/>
+    <col min="27" max="27" width="7.54545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1047,13 +1147,73 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>2298</v>
@@ -1070,13 +1230,73 @@
       <c r="G2">
         <v>80</v>
       </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2">
+        <v>120.3</v>
+      </c>
+      <c r="J2">
+        <v>103500</v>
+      </c>
+      <c r="K2">
+        <v>52.2</v>
+      </c>
+      <c r="L2">
+        <v>20.8</v>
+      </c>
+      <c r="M2">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2">
+        <v>7</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2">
+        <v>25</v>
+      </c>
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2">
+        <v>1074</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>2341</v>
@@ -1093,13 +1313,73 @@
       <c r="G3">
         <v>80</v>
       </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3">
+        <v>164.2</v>
+      </c>
+      <c r="J3">
+        <v>141200</v>
+      </c>
+      <c r="K3">
+        <v>63.8</v>
+      </c>
+      <c r="L3">
+        <v>28.5</v>
+      </c>
+      <c r="M3">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3">
+        <v>37.6</v>
+      </c>
+      <c r="S3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3">
+        <v>7</v>
+      </c>
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3">
+        <v>32</v>
+      </c>
+      <c r="X3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA3">
+        <v>1228</v>
+      </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>2521</v>
@@ -1116,13 +1396,73 @@
       <c r="G4">
         <v>80</v>
       </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4">
+        <v>217.9</v>
+      </c>
+      <c r="J4">
+        <v>187400</v>
+      </c>
+      <c r="K4">
+        <v>91.3</v>
+      </c>
+      <c r="L4">
+        <v>37.8</v>
+      </c>
+      <c r="M4">
+        <v>46.8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4">
+        <v>52.3</v>
+      </c>
+      <c r="S4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4">
+        <v>14</v>
+      </c>
+      <c r="U4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4">
+        <v>42</v>
+      </c>
+      <c r="X4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA4">
+        <v>1372</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>2519</v>
@@ -1139,13 +1479,73 @@
       <c r="G5">
         <v>100</v>
       </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>285.8</v>
+      </c>
+      <c r="J5">
+        <v>245700</v>
+      </c>
+      <c r="K5">
+        <v>113.6</v>
+      </c>
+      <c r="L5">
+        <v>49.1</v>
+      </c>
+      <c r="M5">
+        <v>60</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>66.1</v>
+      </c>
+      <c r="S5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5">
+        <v>14</v>
+      </c>
+      <c r="U5" t="s">
+        <v>34</v>
+      </c>
+      <c r="V5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5">
+        <v>56</v>
+      </c>
+      <c r="X5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA5">
+        <v>1614</v>
+      </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>2611</v>
@@ -1162,13 +1562,73 @@
       <c r="G6">
         <v>100</v>
       </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6">
+        <v>313.7</v>
+      </c>
+      <c r="J6">
+        <v>269700</v>
+      </c>
+      <c r="K6">
+        <v>122.2</v>
+      </c>
+      <c r="L6">
+        <v>53.9</v>
+      </c>
+      <c r="M6">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6">
+        <v>71.3</v>
+      </c>
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6">
+        <v>16</v>
+      </c>
+      <c r="U6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6">
+        <v>62</v>
+      </c>
+      <c r="X6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA6">
+        <v>1766</v>
+      </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>2813</v>
@@ -1185,13 +1645,73 @@
       <c r="G7">
         <v>100</v>
       </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7">
+        <v>369.7</v>
+      </c>
+      <c r="J7">
+        <v>317900</v>
+      </c>
+      <c r="K7">
+        <v>144</v>
+      </c>
+      <c r="L7">
+        <v>64</v>
+      </c>
+      <c r="M7">
+        <v>74</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7">
+        <v>85.2</v>
+      </c>
+      <c r="S7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7">
+        <v>16</v>
+      </c>
+      <c r="U7" t="s">
+        <v>34</v>
+      </c>
+      <c r="V7" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7">
+        <v>75</v>
+      </c>
+      <c r="X7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA7">
+        <v>1872</v>
+      </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>2811</v>
@@ -1208,13 +1728,73 @@
       <c r="G8">
         <v>100</v>
       </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>444.3</v>
+      </c>
+      <c r="J8">
+        <v>367500</v>
+      </c>
+      <c r="K8">
+        <v>166.8</v>
+      </c>
+      <c r="L8">
+        <v>77</v>
+      </c>
+      <c r="M8">
+        <v>94</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8">
+        <v>98.4</v>
+      </c>
+      <c r="S8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T8">
+        <v>18</v>
+      </c>
+      <c r="U8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W8">
+        <v>85</v>
+      </c>
+      <c r="X8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA8">
+        <v>2017</v>
+      </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>3223</v>
@@ -1231,13 +1811,73 @@
       <c r="G9">
         <v>125</v>
       </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>464.4</v>
+      </c>
+      <c r="J9">
+        <v>397800</v>
+      </c>
+      <c r="K9">
+        <v>179.9</v>
+      </c>
+      <c r="L9">
+        <v>79.6</v>
+      </c>
+      <c r="M9">
+        <v>98</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9">
+        <v>105.5</v>
+      </c>
+      <c r="S9" t="s">
+        <v>33</v>
+      </c>
+      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="U9" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9">
+        <v>90</v>
+      </c>
+      <c r="X9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA9">
+        <v>2118</v>
+      </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>3322</v>
@@ -1254,13 +1894,73 @@
       <c r="G10">
         <v>125</v>
       </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10">
+        <v>521.3</v>
+      </c>
+      <c r="J10">
+        <v>438000</v>
+      </c>
+      <c r="K10">
+        <v>196.8</v>
+      </c>
+      <c r="L10">
+        <v>90.3</v>
+      </c>
+      <c r="M10">
+        <v>110.5</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10">
+        <v>116.1</v>
+      </c>
+      <c r="S10" t="s">
+        <v>33</v>
+      </c>
+      <c r="T10">
+        <v>20</v>
+      </c>
+      <c r="U10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10">
+        <v>95</v>
+      </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA10">
+        <v>2525</v>
+      </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>3511</v>
@@ -1277,13 +1977,73 @@
       <c r="G11">
         <v>150</v>
       </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11">
+        <v>606.1</v>
+      </c>
+      <c r="J11">
+        <v>521200</v>
+      </c>
+      <c r="K11">
+        <v>218.4</v>
+      </c>
+      <c r="L11">
+        <v>105</v>
+      </c>
+      <c r="M11">
+        <v>122.7</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11">
+        <v>129</v>
+      </c>
+      <c r="S11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T11">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>34</v>
+      </c>
+      <c r="V11" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11">
+        <v>115</v>
+      </c>
+      <c r="X11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA11">
+        <v>2923</v>
+      </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>3669</v>
@@ -1300,13 +2060,73 @@
       <c r="G12">
         <v>150</v>
       </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12">
+        <v>672.6</v>
+      </c>
+      <c r="J12">
+        <v>578500</v>
+      </c>
+      <c r="K12">
+        <v>252</v>
+      </c>
+      <c r="L12">
+        <v>116.5</v>
+      </c>
+      <c r="M12">
+        <v>142.5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12">
+        <v>150.1</v>
+      </c>
+      <c r="S12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T12">
+        <v>23</v>
+      </c>
+      <c r="U12" t="s">
+        <v>34</v>
+      </c>
+      <c r="V12" t="s">
+        <v>35</v>
+      </c>
+      <c r="W12">
+        <v>125</v>
+      </c>
+      <c r="X12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA12">
+        <v>3217</v>
+      </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>3766</v>
@@ -1323,13 +2143,73 @@
       <c r="G13">
         <v>150</v>
       </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13">
+        <v>724</v>
+      </c>
+      <c r="J13">
+        <v>622700</v>
+      </c>
+      <c r="K13">
+        <v>291.6</v>
+      </c>
+      <c r="L13">
+        <v>125.5</v>
+      </c>
+      <c r="M13">
+        <v>154.5</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13">
+        <v>168.1</v>
+      </c>
+      <c r="S13" t="s">
+        <v>33</v>
+      </c>
+      <c r="T13">
+        <v>28</v>
+      </c>
+      <c r="U13" t="s">
+        <v>34</v>
+      </c>
+      <c r="V13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13">
+        <v>135</v>
+      </c>
+      <c r="X13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA13">
+        <v>3768</v>
+      </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>3820</v>
@@ -1345,11 +2225,70 @@
       </c>
       <c r="G14">
         <v>150</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14">
+        <v>796.6</v>
+      </c>
+      <c r="J14">
+        <v>685100</v>
+      </c>
+      <c r="K14">
+        <v>299.4</v>
+      </c>
+      <c r="L14">
+        <v>138</v>
+      </c>
+      <c r="M14">
+        <v>69</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14">
+        <v>178.6</v>
+      </c>
+      <c r="S14" t="s">
+        <v>33</v>
+      </c>
+      <c r="T14">
+        <v>28</v>
+      </c>
+      <c r="U14" t="s">
+        <v>34</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14">
+        <v>145</v>
+      </c>
+      <c r="X14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14">
+        <v>4120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>